--- a/iraq-products-test.xlsx
+++ b/iraq-products-test.xlsx
@@ -8,11 +8,15 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="المنتجات" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="ملخص المجموعات" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="المنتجات الأساسية" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="منتجات التيست الأولى" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="ممتاز وجيد" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ملخص المجموعات" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">المنتجات!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'المنتجات الأساسية'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'ممتاز وجيد'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'منتجات التيست الأولى'!$4:$4</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,178 +27,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="F8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F30" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F37" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F54" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F59" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F70" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="FreeSans"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">أقل ربح = </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: أقل سعر بيع هو نفس سعر المنتج، فلازم تبيع بسعر أعلى عشان تكسب.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="149">
   <si>
     <t xml:space="preserve">منتجات تيست السوق العراقي  ·  Taager</t>
   </si>
@@ -218,12 +52,6 @@
   </si>
   <si>
     <t xml:space="preserve">أقل ربح (د.ع)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خصم القطعتين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خصومات الكمية حتى</t>
   </si>
   <si>
     <t xml:space="preserve">نسبة التأكيد</t>
@@ -245,9 +73,6 @@
     <t xml:space="preserve">ملاحظات</t>
   </si>
   <si>
-    <t xml:space="preserve">السكرين شوت</t>
-  </si>
-  <si>
     <t xml:space="preserve">مكنسة تنظيف منزلي Acarid Remover</t>
   </si>
   <si>
@@ -257,9 +82,6 @@
     <t xml:space="preserve">ممتاز</t>
   </si>
   <si>
-    <t xml:space="preserve">143306</t>
-  </si>
-  <si>
     <t xml:space="preserve">المكنسة القابلة لإعادة الشحن الحديثة 3 في 1</t>
   </si>
   <si>
@@ -269,66 +91,42 @@
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">143243</t>
-  </si>
-  <si>
     <t xml:space="preserve">المكنسة القابلة لإعادة الشحن 3 في 1 ضمان 6 أشهر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303MKNN99</t>
   </si>
   <si>
-    <t xml:space="preserve">143435</t>
-  </si>
-  <si>
     <t xml:space="preserve">مكنسة روبوت Smart Home ضمان 6 أشهر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303ROHM99</t>
   </si>
   <si>
-    <t xml:space="preserve">143410</t>
-  </si>
-  <si>
     <t xml:space="preserve">مكنسة كهربائية لاسلكية محمولة 2 في 1 ضمان عام</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303MALA99</t>
   </si>
   <si>
-    <t xml:space="preserve">مازالت المنصة تجمع إحصائيات المنتج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143558</t>
-  </si>
-  <si>
     <t xml:space="preserve">المكنسة الكهربائية الحديثة ضمان 6 أشهر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303ACSS99</t>
   </si>
   <si>
-    <t xml:space="preserve">143607</t>
-  </si>
-  <si>
     <t xml:space="preserve">المكنسة الكهربائية اللاسلكية متعددة الاستخدامات GUFY</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030304GUFY99</t>
   </si>
   <si>
-    <t xml:space="preserve">143537</t>
-  </si>
-  <si>
     <t xml:space="preserve">مكنسة تنظيف السجاد و المفروشات جاف ورطب</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030304TAZT99</t>
   </si>
   <si>
-    <t xml:space="preserve">143511</t>
-  </si>
-  <si>
     <t xml:space="preserve">جهاز تنظيف بالبخار بالضغط العالي</t>
   </si>
   <si>
@@ -338,384 +136,312 @@
     <t xml:space="preserve">جيد</t>
   </si>
   <si>
-    <t xml:space="preserve">143015</t>
-  </si>
-  <si>
     <t xml:space="preserve">جهاز تنظيف بالبخار بالضغط العالي شكل دائري</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303BOJH99</t>
   </si>
   <si>
-    <t xml:space="preserve">143633</t>
-  </si>
-  <si>
     <t xml:space="preserve">خلاط Silver Crest + طاحونة ضمان 6 أشهر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401CILV99</t>
   </si>
   <si>
-    <t xml:space="preserve">143453</t>
-  </si>
-  <si>
     <t xml:space="preserve">محضرة الطعام Olympia أكبر حجم 8 لتر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ALMN99</t>
   </si>
   <si>
-    <t xml:space="preserve">143359</t>
-  </si>
-  <si>
     <t xml:space="preserve">محضرة الطعام Olympia 8 لتر + ضمان 6 شهور (عرض مجمّع)</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030501MNOI99</t>
   </si>
   <si>
-    <t xml:space="preserve">مازالت المنصة تجمع إحصائيات المنتج · عرض مجمّع: IQ030401ALMN99 + IQ030101DFLM99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143213</t>
-  </si>
-  <si>
     <t xml:space="preserve">محضرة الطعام المتكاملة 10 في 1</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ROPM99</t>
   </si>
   <si>
-    <t xml:space="preserve">143100</t>
-  </si>
-  <si>
     <t xml:space="preserve">مفرمة اللحوم و الخضروات الحديثة 3 لتر</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401MOGH99</t>
   </si>
   <si>
-    <t xml:space="preserve">143032</t>
-  </si>
-  <si>
     <t xml:space="preserve">قطاعة الخضروات الحديثة</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ATTA99</t>
   </si>
   <si>
-    <t xml:space="preserve">143232</t>
-  </si>
-  <si>
     <t xml:space="preserve">قطاعة الخضروات الحديثة تعمل بالشحن Denx</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401KHOD99</t>
   </si>
   <si>
-    <t xml:space="preserve">143654</t>
-  </si>
-  <si>
     <t xml:space="preserve">محضرة الخضروات الحديثة</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ATMO99</t>
   </si>
   <si>
-    <t xml:space="preserve">143421</t>
-  </si>
-  <si>
     <t xml:space="preserve">مفرمة اللحوم الكهربائية ENZO</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ENZO99</t>
   </si>
   <si>
-    <t xml:space="preserve">143518</t>
-  </si>
-  <si>
     <t xml:space="preserve">جدر تسوية الطعام الكهربائيه</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030404ZPY099</t>
   </si>
   <si>
-    <t xml:space="preserve">143138</t>
-  </si>
-  <si>
     <t xml:space="preserve">موقد 4 عيون بستاند</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401MOKD99</t>
   </si>
   <si>
-    <t xml:space="preserve">142943</t>
-  </si>
-  <si>
     <t xml:space="preserve">غالق الأبواب السحري</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303KHLK99</t>
   </si>
   <si>
-    <t xml:space="preserve">143746</t>
-  </si>
-  <si>
     <t xml:space="preserve">زاوية حمام 4 دور</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030106ZAWW99</t>
   </si>
   <si>
-    <t xml:space="preserve">143737</t>
-  </si>
-  <si>
     <t xml:space="preserve">مجفف أحذية</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303MAGF99</t>
   </si>
   <si>
-    <t xml:space="preserve">143046</t>
-  </si>
-  <si>
     <t xml:space="preserve">صوبه منضدية مودكس</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030401ASRS99</t>
   </si>
   <si>
-    <t xml:space="preserve">143131</t>
-  </si>
-  <si>
     <t xml:space="preserve">قفل باب ذكي Smart Lock</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030303SMAR99</t>
   </si>
   <si>
-    <t xml:space="preserve">143701</t>
-  </si>
-  <si>
     <t xml:space="preserve">سرير هوائي قابل للنفخ Air Bed Single Size + منفاخ</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030501BEDM99</t>
   </si>
   <si>
-    <t xml:space="preserve">مازالت المنصة تجمع إحصائيات المنتج · عرض مجمّع: IQ030103AIRS99 + IQ050202PUMP99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143155</t>
-  </si>
-  <si>
     <t xml:space="preserve">بلور هواء كبير شحن متعدد الاستخدامات</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050402PLAH99</t>
   </si>
   <si>
-    <t xml:space="preserve">144332</t>
-  </si>
-  <si>
     <t xml:space="preserve">سرير هوائي قابل للنفخ Air Bed Double Size</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030103BEDF99</t>
   </si>
   <si>
-    <t xml:space="preserve">143123</t>
-  </si>
-  <si>
     <t xml:space="preserve">كرسي استراحة هزاز</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030103CORS99</t>
   </si>
   <si>
-    <t xml:space="preserve">143344</t>
-  </si>
-  <si>
     <t xml:space="preserve">مغسلة متحركة سهلة التنقل</t>
   </si>
   <si>
     <t xml:space="preserve">IQ051001QWA99</t>
   </si>
   <si>
-    <t xml:space="preserve">144404</t>
-  </si>
-  <si>
     <t xml:space="preserve">خلايا شمسية للشحن السريع</t>
   </si>
   <si>
     <t xml:space="preserve">IQ010502AHJU99</t>
   </si>
   <si>
-    <t xml:space="preserve">143820</t>
-  </si>
-  <si>
     <t xml:space="preserve">كشاف طاقة شمسية 12 لمبة Solar Sensor Light</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030201KSLK99</t>
   </si>
   <si>
-    <t xml:space="preserve">143503</t>
-  </si>
-  <si>
     <t xml:space="preserve">كشاف خارجي طاقة شمسية مزود بباور بانك 200 وات</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030201KALM99</t>
   </si>
   <si>
-    <t xml:space="preserve">143220</t>
-  </si>
-  <si>
     <t xml:space="preserve">مولد طاقة كهربائية بالطاقة الشمسية و الكهرباء Gizzu</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050402POWR00</t>
   </si>
   <si>
-    <t xml:space="preserve">144453</t>
-  </si>
-  <si>
     <t xml:space="preserve">داش كام 3 كاميرات للسيارة Full HD</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050105DACA99</t>
   </si>
   <si>
-    <t xml:space="preserve">144515</t>
-  </si>
-  <si>
     <t xml:space="preserve">داش كام للسيارة بأربع عدسات</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050101ZHX0099</t>
   </si>
   <si>
-    <t xml:space="preserve">144442</t>
-  </si>
-  <si>
     <t xml:space="preserve">كمبروسر و باوربانك للسيارة</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050101POWS99</t>
   </si>
   <si>
-    <t xml:space="preserve">144551</t>
-  </si>
-  <si>
     <t xml:space="preserve">داش كام 4 كاميرات للسيارة QUAD CAMERA Full HD</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050105QUAD99</t>
   </si>
   <si>
-    <t xml:space="preserve">144523</t>
-  </si>
-  <si>
     <t xml:space="preserve">شاحن بطارية سيارة و الموبايل مع منفاخ للإطارات</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050101JZQP99</t>
   </si>
   <si>
-    <t xml:space="preserve">144433</t>
-  </si>
-  <si>
     <t xml:space="preserve">قفل سيارة ذكي للباركينج</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050101AUTO99</t>
   </si>
   <si>
-    <t xml:space="preserve">144357</t>
-  </si>
-  <si>
     <t xml:space="preserve">أداة تصوير 360 درجة</t>
   </si>
   <si>
     <t xml:space="preserve">IQ010106CAMM99</t>
   </si>
   <si>
-    <t xml:space="preserve">143807</t>
-  </si>
-  <si>
     <t xml:space="preserve">Galaxy Projector USB</t>
   </si>
   <si>
     <t xml:space="preserve">IQ030102LIGH99</t>
   </si>
   <si>
-    <t xml:space="preserve">142955</t>
-  </si>
-  <si>
     <t xml:space="preserve">راوتر محمول 5G</t>
   </si>
   <si>
     <t xml:space="preserve">IQ010501ASNN99</t>
   </si>
   <si>
-    <t xml:space="preserve">143812</t>
-  </si>
-  <si>
     <t xml:space="preserve">بروجكتور USB</t>
   </si>
   <si>
     <t xml:space="preserve">IQ010403USBP99</t>
   </si>
   <si>
-    <t xml:space="preserve">143800</t>
-  </si>
-  <si>
     <t xml:space="preserve">جينرال ايبوكسي (عازل متعدد الاستخدامات)</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050401GENI99</t>
   </si>
   <si>
-    <t xml:space="preserve">144559</t>
-  </si>
-  <si>
     <t xml:space="preserve">المادة السحرية لعزل المياه</t>
   </si>
   <si>
     <t xml:space="preserve">IQ050401BLWA99</t>
   </si>
   <si>
-    <t xml:space="preserve">144348</t>
-  </si>
-  <si>
     <t xml:space="preserve">   دليل القراءة</t>
   </si>
   <si>
     <t xml:space="preserve">●</t>
   </si>
   <si>
-    <t xml:space="preserve">ممتاز / جيد = تقييم المنصة لنسبة التأكيد ونسبة التوصيل. الأخضر الغامق في الأعمدة يعني نسبة أعلى.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— = المنتج لسه مالوش إحصائيات على المنصة (مكتوب في صفحته: مازلنا نعمل على توفير إحصائيات لهذا المنتج).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التسليم المتوقع = نسبة التأكيد × نسبة التوصيل، يعني تقريباً كام طلب من كل 100 طلب هيتسلّم فعلاً. بيتحسب بس لو النسبتين ظاهرين.</t>
+    <t xml:space="preserve">ممتاز / جيد = تقييم المنصة لنسبة التأكيد ونسبة التوصيل. الأخضر الغامق في أعمدة النسب يعني نسبة أعلى، والأصفر أقل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— = المنتج لسه مالوش إحصائيات على المنصة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التسليم المتوقع = نسبة التأكيد × نسبة التوصيل، يعني تقريباً كام طلب من كل 100 طلب هيتسلّم فعلاً.</t>
   </si>
   <si>
     <t xml:space="preserve">أقل ربح باللون الأحمر = 0 د.ع، يعني أقل سعر بيع هو نفس سعر المنتج.</t>
   </si>
   <si>
-    <t xml:space="preserve">خصم القطعتين / خصومات الكمية = عروض الكمية المكتوبة في صفحة المنتج.</t>
+    <t xml:space="preserve">منتجات التيست الأولى  ·  أول دفعة تيست في العراق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 منتجات مختارة من المنتجات الأساسية · علامة ✅ في آخر عمود معناها إن المنتج اتعمل عليه تيست</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تم التيست</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتجات اللي تقييمها ممتاز وجيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل المنتجات اللي ليها إحصائيات على المنصة، مقسّمة حسب التقييم ومرتبة من الأعلى في نسبة التأكيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المجموعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ممتاز  ·  كل النسب الظاهرة ممتازة   ·   11 منتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المكانس الكهربائية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسرّة الهوائية والمنافيخ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منزل متنوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المفارم والقطاعات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السيارات (داش كام وإكسسوارات)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إلكترونيات وتقنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ممتاز وجيد  ·  نسبة ممتازة ونسبة جيدة   ·   7 منتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محضرات الطعام والخلاطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أجهزة التنظيف بالبخار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   جيد  ·  كل النسب الظاهرة جيدة   ·   2 منتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الطاقة الشمسية</t>
   </si>
   <si>
     <t xml:space="preserve">ملخص المجموعات</t>
   </si>
   <si>
-    <t xml:space="preserve">المجموعة</t>
-  </si>
-  <si>
     <t xml:space="preserve">عدد المنتجات</t>
   </si>
   <si>
@@ -740,37 +466,10 @@
     <t xml:space="preserve">أعلى تسليم متوقع</t>
   </si>
   <si>
-    <t xml:space="preserve">المكانس الكهربائية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أجهزة التنظيف بالبخار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محضرات الطعام والخلاطات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المفارم والقطاعات</t>
-  </si>
-  <si>
     <t xml:space="preserve">أجهزة مطبخ أخرى</t>
   </si>
   <si>
-    <t xml:space="preserve">منزل متنوع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسرّة الهوائية والمنافيخ</t>
-  </si>
-  <si>
     <t xml:space="preserve">أثاث وتخييم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الطاقة الشمسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السيارات (داش كام وإكسسوارات)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إلكترونيات وتقنية</t>
   </si>
   <si>
     <t xml:space="preserve">العزل والصيانة</t>
@@ -783,15 +482,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; د.ع&quot;;\-#,##0&quot; د.ع&quot;;\-"/>
     <numFmt numFmtId="166" formatCode="0%;\-0%;\-"/>
-    <numFmt numFmtId="167" formatCode="0&quot; قطع&quot;;;\-"/>
-    <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,29 +594,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF7C3AED"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <color rgb="FF166534"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF475569"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF94A3B8"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -933,14 +609,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFB91C1C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF94A3B8"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -982,14 +650,6 @@
       <sz val="10"/>
       <color rgb="FFC2410C"/>
       <name val="Consolas"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF475569"/>
-      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -1178,21 +838,99 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF7C3AED"/>
+      <sz val="14"/>
+      <color rgb="FF166534"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="FreeSans"/>
-      <family val="2"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF166534"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF1D4ED8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF4338CA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7E22CE"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFB45309"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0F766E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC2410C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0E7490"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFA16207"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1309,7 +1047,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7E22CE"/>
-        <bgColor rgb="FF7C3AED"/>
+        <bgColor rgb="FF4338CA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1428,7 +1166,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1473,19 +1211,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1493,12 +1223,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1517,19 +1243,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1537,15 +1259,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1553,47 +1271,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1601,27 +1299,23 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1629,11 +1323,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1641,11 +1335,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1653,11 +1347,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1669,7 +1363,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1677,11 +1371,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1689,11 +1383,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1701,11 +1395,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1713,115 +1407,163 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="44" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="44" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1851,7 +1593,7 @@
       <rgbColor rgb="FF7E22CE"/>
       <rgbColor rgb="FF0F766E"/>
       <rgbColor rgb="FFD5DBE3"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF475569"/>
       <rgbColor rgb="FFE2E8F0"/>
       <rgbColor rgb="FFB91C1C"/>
       <rgbColor rgb="FFFEF9C3"/>
@@ -1864,7 +1606,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFF1F5F9"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF7C3AED"/>
+      <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF0E7490"/>
       <rgbColor rgb="FF0000FF"/>
@@ -1882,10 +1624,10 @@
       <rgbColor rgb="FFFAFBFC"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF475569"/>
+      <rgbColor rgb="FF64748B"/>
       <rgbColor rgb="FF94A3B8"/>
       <rgbColor rgb="FF166534"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF16A34A"/>
       <rgbColor rgb="FF0F172A"/>
       <rgbColor rgb="FF334155"/>
       <rgbColor rgb="FFC2410C"/>
@@ -2075,9 +1817,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1E293B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2086,12 +1829,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2109,9 +1849,6 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2128,9 +1865,6 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -2168,15 +1902,6 @@
       </c>
       <c r="L4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2195,19 +1920,16 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>18000</v>
@@ -2219,81 +1941,67 @@
         <v>3000</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="13" t="n">
         <v>0.83</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>19</v>
+      <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I6),ISNUMBER(K6)),I6*K6,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G6),ISNUMBER(I6)),G6*I6,"")</f>
         <v>0.5893</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="17" t="s">
-        <v>20</v>
-      </c>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>21</v>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" s="16" t="n">
         <v>33000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="17" t="n">
         <v>36000</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="18" t="n">
         <v>3000</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="24" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.79</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="22"/>
-      <c r="L7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I7),ISNUMBER(K7)),I7*K7,"")</f>
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G7),ISNUMBER(I7)),G7*I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>34000</v>
@@ -2301,79 +2009,69 @@
       <c r="E8" s="9" t="n">
         <v>34000</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="13" t="n">
+      <c r="G8" s="11" t="n">
         <v>0.61</v>
       </c>
-      <c r="J8" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I8),ISNUMBER(K8)),I8*K8,"")</f>
+      <c r="H8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G8),ISNUMBER(I8)),G8*I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="17" t="s">
-        <v>27</v>
-      </c>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>28</v>
+      <c r="B9" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" s="16" t="n">
         <v>36000</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="17" t="n">
         <v>39000</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="18" t="n">
         <v>3000</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.63</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I9),ISNUMBER(K9)),I9*K9,"")</f>
+      <c r="H9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G9),ISNUMBER(I9)),G9*I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28" t="s">
-        <v>30</v>
-      </c>
+      <c r="L9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>45000</v>
@@ -2384,80 +2082,62 @@
       <c r="F10" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I10),ISNUMBER(K10)),I10*K10,"")</f>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G10),ISNUMBER(I10)),G10*I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>34</v>
-      </c>
+      <c r="L10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>35</v>
+      <c r="B11" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>45500</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="17" t="n">
         <v>45500</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="35" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H11" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I11),ISNUMBER(K11)),I11*K11,"")</f>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G11),ISNUMBER(I11)),G11*I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="28" t="s">
-        <v>37</v>
-      </c>
+      <c r="L11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>79000</v>
@@ -2468,97 +2148,80 @@
       <c r="F12" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I12),ISNUMBER(K12)),I12*K12,"")</f>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G12),ISNUMBER(I12)),G12*I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>40</v>
-      </c>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>41</v>
+      <c r="B13" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>101000</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="17" t="n">
         <v>101000</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I13),ISNUMBER(K13)),I13*K13,"")</f>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G13),ISNUMBER(I13)),G13*I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" s="28" t="s">
-        <v>43</v>
-      </c>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38" t="str">
+      <c r="A15" s="28" t="str">
         <f aca="false">"   أجهزة التنظيف بالبخار   ·   "&amp;COUNTA(B16:B17)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D16:D17),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D16:D17),"#,##0")&amp;" د.ع"</f>
         <v>   أجهزة التنظيف بالبخار   ·   2 منتجات   ·   السعر من 37,000 إلى 47,000 د.ع</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="n">
+      <c r="A16" s="29" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>33</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>37000</v>
@@ -2570,102 +2233,83 @@
         <v>3000</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="41" t="s">
-        <v>46</v>
+      <c r="H16" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I16),ISNUMBER(K16)),I16*K16,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G16),ISNUMBER(I16)),G16*I16,"")</f>
         <v>0.31</v>
       </c>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17" t="s">
-        <v>47</v>
-      </c>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="19" t="n">
+      <c r="B17" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="16" t="n">
         <v>47000</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="17" t="n">
         <v>50000</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="18" t="n">
         <v>3000</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I17),ISNUMBER(K17)),I17*K17,"")</f>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G17),ISNUMBER(I17)),G17*I17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="28" t="s">
-        <v>50</v>
-      </c>
+      <c r="L17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="str">
+      <c r="A19" s="32" t="str">
         <f aca="false">"   محضرات الطعام والخلاطات   ·   "&amp;COUNTA(B20:B23)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D20:D23),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D20:D23),"#,##0")&amp;" د.ع"</f>
         <v>   محضرات الطعام والخلاطات   ·   4 منتجات   ·   السعر من 26,500 إلى 88,500 د.ع</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43" t="n">
+      <c r="A20" s="33" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>52</v>
+        <v>37</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>38</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>26500</v>
@@ -2677,87 +2321,69 @@
         <v>2000</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="13" t="n">
         <v>0.56</v>
       </c>
-      <c r="J20" s="41" t="s">
-        <v>46</v>
+      <c r="H20" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I20),ISNUMBER(K20)),I20*K20,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G20),ISNUMBER(I20)),G20*I20,"")</f>
         <v>0.3472</v>
       </c>
-      <c r="N20" s="16"/>
-      <c r="O20" s="17" t="s">
-        <v>53</v>
-      </c>
+      <c r="L20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="n">
+      <c r="A21" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="19" t="n">
+      <c r="B21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="16" t="n">
         <v>39000</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G21" s="35" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="24" t="n">
+      <c r="G21" s="19" t="n">
         <v>0.53</v>
       </c>
-      <c r="J21" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="24" t="n">
+      <c r="H21" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="19" t="n">
         <v>0.69</v>
       </c>
-      <c r="L21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I21),ISNUMBER(K21)),I21*K21,"")</f>
+      <c r="J21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G21),ISNUMBER(I21)),G21*I21,"")</f>
         <v>0.3657</v>
       </c>
-      <c r="N21" s="27"/>
-      <c r="O21" s="28" t="s">
-        <v>56</v>
-      </c>
+      <c r="L21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="n">
+      <c r="A22" s="33" t="n">
         <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>58</v>
+        <v>41</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>42</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>43000</v>
@@ -2768,101 +2394,80 @@
       <c r="F22" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="30"/>
-      <c r="L22" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I22),ISNUMBER(K22)),I22*K22,"")</f>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G22),ISNUMBER(I22)),G22*I22,"")</f>
         <v/>
       </c>
-      <c r="N22" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="O22" s="17" t="s">
-        <v>60</v>
-      </c>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="n">
+      <c r="A23" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="19" t="n">
+      <c r="B23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="16" t="n">
         <v>88500</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="17" t="n">
         <v>90500</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G23" s="35" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H23" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M23" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I23),ISNUMBER(K23)),I23*K23,"")</f>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="20"/>
+      <c r="J23" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G23),ISNUMBER(I23)),G23*I23,"")</f>
         <v/>
       </c>
-      <c r="N23" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" s="28" t="s">
-        <v>63</v>
-      </c>
+      <c r="L23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="str">
+      <c r="A25" s="35" t="str">
         <f aca="false">"   المفارم والقطاعات   ·   "&amp;COUNTA(B26:B30)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D26:D30),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D26:D30),"#,##0")&amp;" د.ع"</f>
         <v>   المفارم والقطاعات   ·   5 منتجات   ·   السعر من 21,000 إلى 59,000 د.ع</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="n">
+      <c r="A26" s="36" t="n">
         <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>46</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>21000</v>
@@ -2874,85 +2479,67 @@
         <v>3000</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="13" t="n">
         <v>0.51</v>
       </c>
-      <c r="J26" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="30"/>
-      <c r="L26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M26" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I26),ISNUMBER(K26)),I26*K26,"")</f>
+      <c r="H26" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="25"/>
+      <c r="J26" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G26),ISNUMBER(I26)),G26*I26,"")</f>
         <v/>
       </c>
-      <c r="N26" s="16"/>
-      <c r="O26" s="17" t="s">
-        <v>66</v>
-      </c>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="47" t="n">
+      <c r="A27" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="19" t="n">
+      <c r="B27" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="16" t="n">
         <v>29000</v>
       </c>
-      <c r="E27" s="20" t="n">
+      <c r="E27" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="18" t="n">
         <v>3000</v>
       </c>
-      <c r="G27" s="35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H27" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" s="24" t="n">
+      <c r="G27" s="19" t="n">
         <v>0.63</v>
       </c>
-      <c r="J27" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="24" t="n">
+      <c r="H27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="19" t="n">
         <v>0.67</v>
       </c>
-      <c r="L27" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I27),ISNUMBER(K27)),I27*K27,"")</f>
+      <c r="J27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G27),ISNUMBER(I27)),G27*I27,"")</f>
         <v>0.4221</v>
       </c>
-      <c r="N27" s="27"/>
-      <c r="O27" s="28" t="s">
-        <v>69</v>
-      </c>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="47" t="n">
+      <c r="A28" s="36" t="n">
         <v>17</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>71</v>
+        <v>49</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>50</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>33000</v>
@@ -2963,80 +2550,66 @@
       <c r="F28" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="30"/>
-      <c r="L28" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M28" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I28),ISNUMBER(K28)),I28*K28,"")</f>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G28),ISNUMBER(I28)),G28*I28,"")</f>
         <v/>
       </c>
-      <c r="N28" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28" s="17" t="s">
-        <v>72</v>
-      </c>
+      <c r="L28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47" t="n">
+      <c r="A29" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="19" t="n">
+      <c r="B29" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="16" t="n">
         <v>40500</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="17" t="n">
         <v>42500</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I29" s="24" t="n">
+      <c r="G29" s="19" t="n">
         <v>0.56</v>
       </c>
-      <c r="J29" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="24" t="n">
+      <c r="H29" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I29),ISNUMBER(K29)),I29*K29,"")</f>
+      <c r="J29" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G29),ISNUMBER(I29)),G29*I29,"")</f>
         <v>0.3248</v>
       </c>
-      <c r="N29" s="27"/>
-      <c r="O29" s="28" t="s">
-        <v>75</v>
-      </c>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="47" t="n">
+      <c r="A30" s="36" t="n">
         <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>54</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>59000</v>
@@ -3044,60 +2617,50 @@
       <c r="E30" s="9" t="n">
         <v>59000</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="30"/>
-      <c r="L30" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I30),ISNUMBER(K30)),I30*K30,"")</f>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="25"/>
+      <c r="J30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G30),ISNUMBER(I30)),G30*I30,"")</f>
         <v/>
       </c>
-      <c r="N30" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="17" t="s">
-        <v>78</v>
-      </c>
+      <c r="L30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="str">
+      <c r="A32" s="38" t="str">
         <f aca="false">"   أجهزة مطبخ أخرى   ·   "&amp;COUNTA(B33:B34)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D33:D34),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D33:D34),"#,##0")&amp;" د.ع"</f>
         <v>   أجهزة مطبخ أخرى   ·   2 منتجات   ·   السعر من 29,000 إلى 60,000 د.ع</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="49"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="39" t="n">
         <v>20</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>80</v>
+        <v>55</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>56</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>29000</v>
@@ -3108,97 +2671,80 @@
       <c r="F33" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="30"/>
-      <c r="L33" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M33" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I33),ISNUMBER(K33)),I33*K33,"")</f>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G33),ISNUMBER(I33)),G33*I33,"")</f>
         <v/>
       </c>
-      <c r="N33" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="17" t="s">
-        <v>81</v>
-      </c>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="n">
+      <c r="A34" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="19" t="n">
+      <c r="B34" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="16" t="n">
         <v>60000</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E34" s="17" t="n">
         <v>62000</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I34),ISNUMBER(K34)),I34*K34,"")</f>
+      <c r="G34" s="20"/>
+      <c r="H34" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="20"/>
+      <c r="J34" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G34),ISNUMBER(I34)),G34*I34,"")</f>
         <v/>
       </c>
-      <c r="N34" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="28" t="s">
-        <v>84</v>
-      </c>
+      <c r="L34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="52" t="str">
+      <c r="A36" s="41" t="str">
         <f aca="false">"   منزل متنوع   ·   "&amp;COUNTA(B37:B41)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D37:D41),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D37:D41),"#,##0")&amp;" د.ع"</f>
         <v>   منزل متنوع   ·   5 منتجات   ·   السعر من 11,500 إلى 59,000 د.ع</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="53" t="n">
+      <c r="A37" s="42" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="54" t="s">
-        <v>86</v>
+        <v>59</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>11500</v>
@@ -3206,87 +2752,65 @@
       <c r="E37" s="9" t="n">
         <v>11500</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I37" s="30"/>
-      <c r="J37" s="32" t="s">
+      <c r="G37" s="25"/>
+      <c r="H37" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="25"/>
+      <c r="J37" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G37),ISNUMBER(I37)),G37*I37,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="42" t="n">
         <v>23</v>
       </c>
-      <c r="K37" s="30"/>
-      <c r="L37" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M37" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I37),ISNUMBER(K37)),I37*K37,"")</f>
+      <c r="B38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G38" s="20"/>
+      <c r="H38" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="20"/>
+      <c r="J38" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G38),ISNUMBER(I38)),G38*I38,"")</f>
         <v/>
       </c>
-      <c r="N37" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="53" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G38" s="35" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H38" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I38" s="22"/>
-      <c r="J38" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I38),ISNUMBER(K38)),I38*K38,"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="28" t="s">
-        <v>90</v>
-      </c>
+      <c r="L38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53" t="n">
+      <c r="A39" s="42" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>92</v>
+        <v>63</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>19000</v>
@@ -3298,81 +2822,65 @@
         <v>2000</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I39" s="13" t="n">
         <v>0.71</v>
       </c>
-      <c r="J39" s="14" t="s">
-        <v>19</v>
+      <c r="H39" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M39" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I39),ISNUMBER(K39)),I39*K39,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G39),ISNUMBER(I39)),G39*I39,"")</f>
         <v>0.4047</v>
       </c>
-      <c r="N39" s="16"/>
-      <c r="O39" s="17" t="s">
-        <v>93</v>
-      </c>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="53" t="n">
+      <c r="A40" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="19" t="n">
+      <c r="B40" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="16" t="n">
         <v>25500</v>
       </c>
-      <c r="E40" s="20" t="n">
+      <c r="E40" s="17" t="n">
         <v>28500</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="18" t="n">
         <v>3000</v>
       </c>
-      <c r="G40" s="22"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I40),ISNUMBER(K40)),I40*K40,"")</f>
+      <c r="G40" s="20"/>
+      <c r="H40" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G40),ISNUMBER(I40)),G40*I40,"")</f>
         <v/>
       </c>
-      <c r="N40" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O40" s="28" t="s">
-        <v>96</v>
-      </c>
+      <c r="L40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="53" t="n">
+      <c r="A41" s="42" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="54" t="s">
-        <v>98</v>
+        <v>67</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>68</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>59000</v>
@@ -3383,57 +2891,47 @@
       <c r="F41" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="30"/>
-      <c r="L41" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I41),ISNUMBER(K41)),I41*K41,"")</f>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="25"/>
+      <c r="J41" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G41),ISNUMBER(I41)),G41*I41,"")</f>
         <v/>
       </c>
-      <c r="N41" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O41" s="17" t="s">
-        <v>99</v>
-      </c>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="55" t="str">
+      <c r="A43" s="44" t="str">
         <f aca="false">"   الأسرّة الهوائية والمنافيخ   ·   "&amp;COUNTA(B44:B46)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D44:D46),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D44:D46),"#,##0")&amp;" د.ع"</f>
         <v>   الأسرّة الهوائية والمنافيخ   ·   3 منتجات   ·   السعر من 41,000 إلى 62,500 د.ع</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="55"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="56" t="n">
+      <c r="A44" s="45" t="n">
         <v>27</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="57" t="s">
-        <v>101</v>
+        <v>69</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>70</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>41000</v>
@@ -3444,76 +2942,64 @@
       <c r="F44" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G44" s="30"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K44" s="30"/>
-      <c r="L44" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I44),ISNUMBER(K44)),I44*K44,"")</f>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="25"/>
+      <c r="J44" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G44),ISNUMBER(I44)),G44*I44,"")</f>
         <v/>
       </c>
-      <c r="N44" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="O44" s="17" t="s">
-        <v>103</v>
-      </c>
+      <c r="L44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="56" t="n">
+      <c r="A45" s="45" t="n">
         <v>28</v>
       </c>
-      <c r="B45" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" s="19" t="n">
+      <c r="B45" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="16" t="n">
         <v>48000</v>
       </c>
-      <c r="E45" s="20" t="n">
+      <c r="E45" s="17" t="n">
         <v>50000</v>
       </c>
-      <c r="F45" s="21" t="n">
+      <c r="F45" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G45" s="22"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="24" t="n">
+      <c r="G45" s="19" t="n">
         <v>0.76</v>
       </c>
-      <c r="J45" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I45),ISNUMBER(K45)),I45*K45,"")</f>
+      <c r="H45" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="20"/>
+      <c r="J45" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G45),ISNUMBER(I45)),G45*I45,"")</f>
         <v/>
       </c>
-      <c r="N45" s="27"/>
-      <c r="O45" s="28" t="s">
-        <v>106</v>
-      </c>
+      <c r="L45" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="56" t="n">
+      <c r="A46" s="45" t="n">
         <v>29</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>74</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>62500</v>
@@ -3524,57 +3010,47 @@
       <c r="F46" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="G46" s="30"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46" s="30"/>
-      <c r="L46" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I46),ISNUMBER(K46)),I46*K46,"")</f>
+      <c r="G46" s="25"/>
+      <c r="H46" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="25"/>
+      <c r="J46" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G46),ISNUMBER(I46)),G46*I46,"")</f>
         <v/>
       </c>
-      <c r="N46" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O46" s="17" t="s">
-        <v>109</v>
-      </c>
+      <c r="L46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58" t="str">
+      <c r="A48" s="47" t="str">
         <f aca="false">"   أثاث وتخييم   ·   "&amp;COUNTA(B49:B50)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D49:D50),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D49:D50),"#,##0")&amp;" د.ع"</f>
         <v>   أثاث وتخييم   ·   2 منتجات   ·   السعر من 72,000 إلى 81,000 د.ع</v>
       </c>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="59" t="n">
+      <c r="A49" s="48" t="n">
         <v>30</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" s="60" t="s">
-        <v>111</v>
+        <v>75</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>76</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>72000</v>
@@ -3585,105 +3061,80 @@
       <c r="F49" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="30"/>
-      <c r="J49" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="30"/>
-      <c r="L49" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I49),ISNUMBER(K49)),I49*K49,"")</f>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="25"/>
+      <c r="J49" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G49),ISNUMBER(I49)),G49*I49,"")</f>
         <v/>
       </c>
-      <c r="N49" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O49" s="17" t="s">
-        <v>112</v>
-      </c>
+      <c r="L49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="59" t="n">
+      <c r="A50" s="48" t="n">
         <v>31</v>
       </c>
-      <c r="B50" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="19" t="n">
+      <c r="B50" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="16" t="n">
         <v>81000</v>
       </c>
-      <c r="E50" s="20" t="n">
+      <c r="E50" s="17" t="n">
         <v>85000</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="F50" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="G50" s="35" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="H50" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="22"/>
-      <c r="J50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="22"/>
-      <c r="L50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M50" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I50),ISNUMBER(K50)),I50*K50,"")</f>
+      <c r="G50" s="20"/>
+      <c r="H50" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="20"/>
+      <c r="J50" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G50),ISNUMBER(I50)),G50*I50,"")</f>
         <v/>
       </c>
-      <c r="N50" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O50" s="28" t="s">
-        <v>115</v>
-      </c>
+      <c r="L50" s="23"/>
     </row>
     <row r="51" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="61" t="str">
+      <c r="A52" s="50" t="str">
         <f aca="false">"   الطاقة الشمسية   ·   "&amp;COUNTA(B53:B56)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D53:D56),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D53:D56),"#,##0")&amp;" د.ع"</f>
         <v>   الطاقة الشمسية   ·   4 منتجات   ·   السعر من 22,000 إلى 212,000 د.ع</v>
       </c>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
-      <c r="L52" s="61"/>
-      <c r="M52" s="61"/>
-      <c r="N52" s="61"/>
-      <c r="O52" s="61"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="50"/>
+      <c r="K52" s="50"/>
+      <c r="L52" s="50"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="62" t="n">
+      <c r="A53" s="51" t="n">
         <v>32</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="63" t="s">
-        <v>117</v>
+        <v>79</v>
+      </c>
+      <c r="C53" s="52" t="s">
+        <v>80</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>22000</v>
@@ -3694,78 +3145,66 @@
       <c r="F53" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G53" s="30"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K53" s="30"/>
-      <c r="L53" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I53),ISNUMBER(K53)),I53*K53,"")</f>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="25"/>
+      <c r="J53" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G53),ISNUMBER(I53)),G53*I53,"")</f>
         <v/>
       </c>
-      <c r="N53" s="33" t="s">
+      <c r="L53" s="14"/>
+    </row>
+    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="51" t="n">
         <v>33</v>
       </c>
-      <c r="O53" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="62" t="n">
-        <v>33</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="63" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" s="19" t="n">
+      <c r="B54" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="16" t="n">
         <v>33000</v>
       </c>
-      <c r="E54" s="20" t="n">
+      <c r="E54" s="17" t="n">
         <v>33000</v>
       </c>
-      <c r="F54" s="34" t="n">
+      <c r="F54" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="22"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="24" t="n">
+      <c r="G54" s="19" t="n">
         <v>0.54</v>
       </c>
-      <c r="J54" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="K54" s="24" t="n">
+      <c r="H54" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="19" t="n">
         <v>0.41</v>
       </c>
-      <c r="L54" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="M54" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I54),ISNUMBER(K54)),I54*K54,"")</f>
+      <c r="J54" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K54" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G54),ISNUMBER(I54)),G54*I54,"")</f>
         <v>0.2214</v>
       </c>
-      <c r="N54" s="27"/>
-      <c r="O54" s="28" t="s">
-        <v>121</v>
-      </c>
+      <c r="L54" s="23"/>
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="62" t="n">
+      <c r="A55" s="51" t="n">
         <v>34</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C55" s="63" t="s">
-        <v>123</v>
+        <v>83</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>84</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>33000</v>
@@ -3776,97 +3215,80 @@
       <c r="F55" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G55" s="30"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55" s="30"/>
-      <c r="L55" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M55" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I55),ISNUMBER(K55)),I55*K55,"")</f>
+      <c r="G55" s="25"/>
+      <c r="H55" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="25"/>
+      <c r="J55" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G55),ISNUMBER(I55)),G55*I55,"")</f>
         <v/>
       </c>
-      <c r="N55" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O55" s="17" t="s">
-        <v>124</v>
-      </c>
+      <c r="L55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="62" t="n">
+      <c r="A56" s="51" t="n">
         <v>35</v>
       </c>
-      <c r="B56" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="19" t="n">
+      <c r="B56" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="16" t="n">
         <v>212000</v>
       </c>
-      <c r="E56" s="20" t="n">
+      <c r="E56" s="17" t="n">
         <v>217000</v>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="F56" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="G56" s="22"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K56" s="22"/>
-      <c r="L56" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M56" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I56),ISNUMBER(K56)),I56*K56,"")</f>
+      <c r="G56" s="20"/>
+      <c r="H56" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G56),ISNUMBER(I56)),G56*I56,"")</f>
         <v/>
       </c>
-      <c r="N56" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O56" s="28" t="s">
-        <v>127</v>
-      </c>
+      <c r="L56" s="23"/>
     </row>
     <row r="57" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="64" t="str">
+      <c r="A58" s="53" t="str">
         <f aca="false">"   السيارات (داش كام وإكسسوارات)   ·   "&amp;COUNTA(B59:B64)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D59:D64),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D59:D64),"#,##0")&amp;" د.ع"</f>
         <v>   السيارات (داش كام وإكسسوارات)   ·   6 منتجات   ·   السعر من 30,000 إلى 90,000 د.ع</v>
       </c>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
-      <c r="N58" s="64"/>
-      <c r="O58" s="64"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
     </row>
     <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="65" t="n">
+      <c r="A59" s="54" t="n">
         <v>36</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="66" t="s">
-        <v>129</v>
+        <v>87</v>
+      </c>
+      <c r="C59" s="55" t="s">
+        <v>88</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>30000</v>
@@ -3874,85 +3296,71 @@
       <c r="E59" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="30"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="13" t="n">
+      <c r="G59" s="11" t="n">
         <v>0.63</v>
       </c>
-      <c r="J59" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K59" s="30"/>
-      <c r="L59" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M59" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I59),ISNUMBER(K59)),I59*K59,"")</f>
+      <c r="H59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="25"/>
+      <c r="J59" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G59),ISNUMBER(I59)),G59*I59,"")</f>
         <v/>
       </c>
-      <c r="N59" s="16"/>
-      <c r="O59" s="17" t="s">
-        <v>130</v>
-      </c>
+      <c r="L59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="65" t="n">
+      <c r="A60" s="54" t="n">
         <v>37</v>
       </c>
-      <c r="B60" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="D60" s="19" t="n">
+      <c r="B60" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="16" t="n">
         <v>39000</v>
       </c>
-      <c r="E60" s="20" t="n">
+      <c r="E60" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="F60" s="21" t="n">
+      <c r="F60" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G60" s="35" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H60" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" s="24" t="n">
+      <c r="G60" s="19" t="n">
         <v>0.59</v>
       </c>
-      <c r="J60" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="K60" s="24" t="n">
+      <c r="H60" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60" s="19" t="n">
         <v>0.46</v>
       </c>
-      <c r="L60" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M60" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I60),ISNUMBER(K60)),I60*K60,"")</f>
+      <c r="J60" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G60),ISNUMBER(I60)),G60*I60,"")</f>
         <v>0.2714</v>
       </c>
-      <c r="N60" s="27"/>
-      <c r="O60" s="28" t="s">
-        <v>133</v>
-      </c>
+      <c r="L60" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="65" t="n">
+      <c r="A61" s="54" t="n">
         <v>38</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="66" t="s">
-        <v>135</v>
+        <v>91</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>92</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>42500</v>
@@ -3964,81 +3372,67 @@
         <v>5000</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" s="13" t="n">
         <v>0.64</v>
       </c>
-      <c r="J61" s="14" t="s">
-        <v>19</v>
+      <c r="H61" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J61" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L61" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="M61" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I61),ISNUMBER(K61)),I61*K61,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G61),ISNUMBER(I61)),G61*I61,"")</f>
         <v>0.2688</v>
       </c>
-      <c r="N61" s="16"/>
-      <c r="O61" s="17" t="s">
-        <v>136</v>
-      </c>
+      <c r="L61" s="14"/>
     </row>
     <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="65" t="n">
+      <c r="A62" s="54" t="n">
         <v>39</v>
       </c>
-      <c r="B62" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" s="19" t="n">
+      <c r="B62" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="16" t="n">
         <v>45000</v>
       </c>
-      <c r="E62" s="20" t="n">
+      <c r="E62" s="17" t="n">
         <v>47000</v>
       </c>
-      <c r="F62" s="21" t="n">
+      <c r="F62" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G62" s="22"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="24" t="n">
+      <c r="G62" s="19" t="n">
         <v>0.61</v>
       </c>
-      <c r="J62" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K62" s="22"/>
-      <c r="L62" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M62" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I62),ISNUMBER(K62)),I62*K62,"")</f>
+      <c r="H62" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="20"/>
+      <c r="J62" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G62),ISNUMBER(I62)),G62*I62,"")</f>
         <v/>
       </c>
-      <c r="N62" s="27"/>
-      <c r="O62" s="28" t="s">
-        <v>139</v>
-      </c>
+      <c r="L62" s="23"/>
     </row>
     <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="65" t="n">
+      <c r="A63" s="54" t="n">
         <v>40</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="66" t="s">
-        <v>141</v>
+        <v>95</v>
+      </c>
+      <c r="C63" s="55" t="s">
+        <v>96</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>53500</v>
@@ -4049,101 +3443,88 @@
       <c r="F63" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="G63" s="30"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="13" t="n">
+      <c r="G63" s="11" t="n">
         <v>0.63</v>
       </c>
-      <c r="J63" s="14" t="s">
-        <v>19</v>
+      <c r="H63" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L63" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M63" s="15" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I63),ISNUMBER(K63)),I63*K63,"")</f>
+        <f aca="false">IF(AND(ISNUMBER(G63),ISNUMBER(I63)),G63*I63,"")</f>
         <v>0.315</v>
       </c>
-      <c r="N63" s="16"/>
-      <c r="O63" s="17" t="s">
-        <v>142</v>
-      </c>
+      <c r="L63" s="14"/>
     </row>
     <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="65" t="n">
+      <c r="A64" s="54" t="n">
         <v>41</v>
       </c>
-      <c r="B64" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="D64" s="19" t="n">
+      <c r="B64" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C64" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" s="16" t="n">
         <v>90000</v>
       </c>
-      <c r="E64" s="20" t="n">
+      <c r="E64" s="17" t="n">
         <v>95000</v>
       </c>
-      <c r="F64" s="21" t="n">
+      <c r="F64" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="G64" s="22"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="24" t="n">
+      <c r="G64" s="19" t="n">
         <v>0.71</v>
       </c>
-      <c r="J64" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K64" s="24" t="n">
+      <c r="H64" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="L64" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="M64" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(I64),ISNUMBER(K64)),I64*K64,"")</f>
+      <c r="J64" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K64" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G64),ISNUMBER(I64)),G64*I64,"")</f>
         <v>0.284</v>
       </c>
-      <c r="N64" s="27"/>
-      <c r="O64" s="28" t="s">
-        <v>145</v>
-      </c>
+      <c r="L64" s="23"/>
     </row>
     <row r="65" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="67" t="str">
+      <c r="A66" s="56" t="str">
         <f aca="false">"   إلكترونيات وتقنية   ·   "&amp;COUNTA(B67:B70)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D67:D70),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D67:D70),"#,##0")&amp;" د.ع"</f>
         <v>   إلكترونيات وتقنية   ·   4 منتجات   ·   السعر من 17,000 إلى 38,500 د.ع</v>
       </c>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="67"/>
-      <c r="J66" s="67"/>
-      <c r="K66" s="67"/>
-      <c r="L66" s="67"/>
-      <c r="M66" s="67"/>
-      <c r="N66" s="67"/>
-      <c r="O66" s="67"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
+      <c r="L66" s="56"/>
     </row>
     <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="68" t="n">
+      <c r="A67" s="57" t="n">
         <v>42</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C67" s="69" t="s">
-        <v>147</v>
+        <v>99</v>
+      </c>
+      <c r="C67" s="58" t="s">
+        <v>100</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>17000</v>
@@ -4154,84 +3535,64 @@
       <c r="F67" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="G67" s="11" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" s="30"/>
-      <c r="J67" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K67" s="30"/>
-      <c r="L67" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I67),ISNUMBER(K67)),I67*K67,"")</f>
+      <c r="G67" s="25"/>
+      <c r="H67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="25"/>
+      <c r="J67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K67" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G67),ISNUMBER(I67)),G67*I67,"")</f>
         <v/>
       </c>
-      <c r="N67" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O67" s="17" t="s">
-        <v>148</v>
-      </c>
+      <c r="L67" s="14"/>
     </row>
     <row r="68" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="68" t="n">
+      <c r="A68" s="57" t="n">
         <v>43</v>
       </c>
-      <c r="B68" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" s="69" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" s="19" t="n">
+      <c r="B68" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="16" t="n">
         <v>29500</v>
       </c>
-      <c r="E68" s="20" t="n">
+      <c r="E68" s="17" t="n">
         <v>31500</v>
       </c>
-      <c r="F68" s="21" t="n">
+      <c r="F68" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G68" s="35" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H68" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" s="22"/>
-      <c r="J68" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K68" s="24" t="n">
+      <c r="G68" s="20"/>
+      <c r="H68" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="19" t="n">
         <v>0.67</v>
       </c>
-      <c r="L68" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M68" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I68),ISNUMBER(K68)),I68*K68,"")</f>
+      <c r="J68" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G68),ISNUMBER(I68)),G68*I68,"")</f>
         <v/>
       </c>
-      <c r="N68" s="27"/>
-      <c r="O68" s="28" t="s">
-        <v>151</v>
-      </c>
+      <c r="L68" s="23"/>
     </row>
     <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="68" t="n">
+      <c r="A69" s="57" t="n">
         <v>44</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="69" t="s">
-        <v>153</v>
+        <v>103</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>104</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>34000</v>
@@ -4242,97 +3603,80 @@
       <c r="F69" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G69" s="30"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K69" s="30"/>
-      <c r="L69" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M69" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I69),ISNUMBER(K69)),I69*K69,"")</f>
+      <c r="G69" s="25"/>
+      <c r="H69" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="25"/>
+      <c r="J69" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G69),ISNUMBER(I69)),G69*I69,"")</f>
         <v/>
       </c>
-      <c r="N69" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O69" s="17" t="s">
-        <v>154</v>
-      </c>
+      <c r="L69" s="14"/>
     </row>
     <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="68" t="n">
+      <c r="A70" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="B70" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C70" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="D70" s="19" t="n">
+      <c r="B70" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="16" t="n">
         <v>38500</v>
       </c>
-      <c r="E70" s="20" t="n">
+      <c r="E70" s="17" t="n">
         <v>38500</v>
       </c>
-      <c r="F70" s="34" t="n">
+      <c r="F70" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="22"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70" s="22"/>
-      <c r="L70" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M70" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I70),ISNUMBER(K70)),I70*K70,"")</f>
+      <c r="G70" s="20"/>
+      <c r="H70" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="20"/>
+      <c r="J70" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G70),ISNUMBER(I70)),G70*I70,"")</f>
         <v/>
       </c>
-      <c r="N70" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O70" s="28" t="s">
-        <v>157</v>
-      </c>
+      <c r="L70" s="23"/>
     </row>
     <row r="71" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="70" t="str">
+      <c r="A72" s="59" t="str">
         <f aca="false">"   العزل والصيانة   ·   "&amp;COUNTA(B73:B74)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D73:D74),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D73:D74),"#,##0")&amp;" د.ع"</f>
         <v>   العزل والصيانة   ·   2 منتجات   ·   السعر من 14,000 إلى 15,500 د.ع</v>
       </c>
-      <c r="B72" s="70"/>
-      <c r="C72" s="70"/>
-      <c r="D72" s="70"/>
-      <c r="E72" s="70"/>
-      <c r="F72" s="70"/>
-      <c r="G72" s="70"/>
-      <c r="H72" s="70"/>
-      <c r="I72" s="70"/>
-      <c r="J72" s="70"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="70"/>
-      <c r="M72" s="70"/>
-      <c r="N72" s="70"/>
-      <c r="O72" s="70"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="59"/>
+      <c r="J72" s="59"/>
+      <c r="K72" s="59"/>
+      <c r="L72" s="59"/>
     </row>
     <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="71" t="n">
+      <c r="A73" s="60" t="n">
         <v>46</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73" s="72" t="s">
-        <v>159</v>
+        <v>107</v>
+      </c>
+      <c r="C73" s="61" t="s">
+        <v>108</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>14000</v>
@@ -4343,224 +3687,165 @@
       <c r="F73" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="G73" s="11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" s="30"/>
-      <c r="J73" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K73" s="30"/>
-      <c r="L73" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" s="15" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I73),ISNUMBER(K73)),I73*K73,"")</f>
+      <c r="G73" s="25"/>
+      <c r="H73" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="25"/>
+      <c r="J73" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K73" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G73),ISNUMBER(I73)),G73*I73,"")</f>
         <v/>
       </c>
-      <c r="N73" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O73" s="17" t="s">
-        <v>160</v>
-      </c>
+      <c r="L73" s="14"/>
     </row>
     <row r="74" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="71" t="n">
+      <c r="A74" s="60" t="n">
         <v>47</v>
       </c>
-      <c r="B74" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C74" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="D74" s="19" t="n">
+      <c r="B74" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" s="16" t="n">
         <v>15500</v>
       </c>
-      <c r="E74" s="20" t="n">
+      <c r="E74" s="17" t="n">
         <v>17500</v>
       </c>
-      <c r="F74" s="21" t="n">
+      <c r="F74" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H74" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="I74" s="22"/>
-      <c r="J74" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74" s="22"/>
-      <c r="L74" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(I74),ISNUMBER(K74)),I74*K74,"")</f>
+      <c r="G74" s="20"/>
+      <c r="H74" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="20"/>
+      <c r="J74" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G74),ISNUMBER(I74)),G74*I74,"")</f>
         <v/>
       </c>
-      <c r="N74" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O74" s="28" t="s">
-        <v>163</v>
-      </c>
+      <c r="L74" s="23"/>
     </row>
     <row r="75" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="73" t="s">
-        <v>164</v>
-      </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="73"/>
-      <c r="K76" s="73"/>
-      <c r="L76" s="73"/>
-      <c r="M76" s="73"/>
-      <c r="N76" s="73"/>
-      <c r="O76" s="73"/>
+      <c r="A76" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" s="62"/>
+      <c r="C76" s="62"/>
+      <c r="D76" s="62"/>
+      <c r="E76" s="62"/>
+      <c r="F76" s="62"/>
+      <c r="G76" s="62"/>
+      <c r="H76" s="62"/>
+      <c r="I76" s="62"/>
+      <c r="J76" s="62"/>
+      <c r="K76" s="62"/>
+      <c r="L76" s="62"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" s="75" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="75"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="75"/>
-      <c r="F77" s="75"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="75"/>
-      <c r="J77" s="75"/>
-      <c r="K77" s="75"/>
-      <c r="L77" s="75"/>
-      <c r="M77" s="75"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="75"/>
+      <c r="A77" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C77" s="64"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="64"/>
+      <c r="H77" s="64"/>
+      <c r="I77" s="64"/>
+      <c r="J77" s="64"/>
+      <c r="K77" s="64"/>
+      <c r="L77" s="64"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="76" t="s">
-        <v>165</v>
-      </c>
-      <c r="B78" s="75" t="s">
-        <v>167</v>
-      </c>
-      <c r="C78" s="75"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="75"/>
-      <c r="F78" s="75"/>
-      <c r="G78" s="75"/>
-      <c r="H78" s="75"/>
-      <c r="I78" s="75"/>
-      <c r="J78" s="75"/>
-      <c r="K78" s="75"/>
-      <c r="L78" s="75"/>
-      <c r="M78" s="75"/>
-      <c r="N78" s="75"/>
-      <c r="O78" s="75"/>
+      <c r="A78" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="64"/>
+      <c r="J78" s="64"/>
+      <c r="K78" s="64"/>
+      <c r="L78" s="64"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B79" s="75" t="s">
-        <v>168</v>
-      </c>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
-      <c r="E79" s="75"/>
-      <c r="F79" s="75"/>
-      <c r="G79" s="75"/>
-      <c r="H79" s="75"/>
-      <c r="I79" s="75"/>
-      <c r="J79" s="75"/>
-      <c r="K79" s="75"/>
-      <c r="L79" s="75"/>
-      <c r="M79" s="75"/>
-      <c r="N79" s="75"/>
-      <c r="O79" s="75"/>
+      <c r="A79" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C79" s="64"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="64"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="64"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="64"/>
+      <c r="L79" s="64"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="78" t="s">
-        <v>165</v>
-      </c>
-      <c r="B80" s="75" t="s">
-        <v>169</v>
-      </c>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
-      <c r="J80" s="75"/>
-      <c r="K80" s="75"/>
-      <c r="L80" s="75"/>
-      <c r="M80" s="75"/>
-      <c r="N80" s="75"/>
-      <c r="O80" s="75"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="B81" s="75" t="s">
-        <v>170</v>
-      </c>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
-      <c r="E81" s="75"/>
-      <c r="F81" s="75"/>
-      <c r="G81" s="75"/>
-      <c r="H81" s="75"/>
-      <c r="I81" s="75"/>
-      <c r="J81" s="75"/>
-      <c r="K81" s="75"/>
-      <c r="L81" s="75"/>
-      <c r="M81" s="75"/>
-      <c r="N81" s="75"/>
-      <c r="O81" s="75"/>
+      <c r="A80" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B80" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64"/>
+      <c r="J80" s="64"/>
+      <c r="K80" s="64"/>
+      <c r="L80" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="A48:O48"/>
-    <mergeCell ref="A52:O52"/>
-    <mergeCell ref="A58:O58"/>
-    <mergeCell ref="A66:O66"/>
-    <mergeCell ref="A72:O72"/>
-    <mergeCell ref="A76:O76"/>
-    <mergeCell ref="B77:O77"/>
-    <mergeCell ref="B78:O78"/>
-    <mergeCell ref="B79:O79"/>
-    <mergeCell ref="B80:O80"/>
-    <mergeCell ref="B81:O81"/>
+  <mergeCells count="19">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A58:L58"/>
+    <mergeCell ref="A66:L66"/>
+    <mergeCell ref="A72:L72"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="B80:L80"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I74">
+  <conditionalFormatting sqref="G5:G74">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.35"/>
@@ -4572,7 +3857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K74">
+  <conditionalFormatting sqref="I5:I74">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.35"/>
@@ -4584,7 +3869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M74">
+  <conditionalFormatting sqref="K5:K74">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.35"/>
@@ -4603,13 +3888,1707 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF16A34A"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="str">
+        <f aca="false">"   المكانس الكهربائية   ·   "&amp;COUNTA(B6:B8)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D6:D8),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D6:D8),"#,##0")&amp;" د.ع"</f>
+        <v>   المكانس الكهربائية   ·   3 منتجات   ·   السعر من 18,000 إلى 36,000 د.ع</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G6),ISNUMBER(I6)),G6*I6,"")</f>
+        <v>0.5893</v>
+      </c>
+      <c r="L6" s="68"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>36000</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G7),ISNUMBER(I7)),G7*I7,"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="69"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G8),ISNUMBER(I8)),G8*I8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="68"/>
+    </row>
+    <row r="9" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="str">
+        <f aca="false">"   أجهزة التنظيف بالبخار   ·   "&amp;COUNTA(B11:B11)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D11:D11),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D11:D11),"#,##0")&amp;" د.ع"</f>
+        <v>   أجهزة التنظيف بالبخار   ·   1 منتجات   ·   السعر من 37,000 إلى 37,000 د.ع</v>
+      </c>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G11),ISNUMBER(I11)),G11*I11,"")</f>
+        <v>0.31</v>
+      </c>
+      <c r="L11" s="68"/>
+    </row>
+    <row r="12" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="str">
+        <f aca="false">"   محضرات الطعام والخلاطات   ·   "&amp;COUNTA(B14:B16)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D14:D16),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D14:D16),"#,##0")&amp;" د.ع"</f>
+        <v>   محضرات الطعام والخلاطات   ·   3 منتجات   ·   السعر من 26,500 إلى 43,000 د.ع</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>26500</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>28500</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G14),ISNUMBER(I14)),G14*I14,"")</f>
+        <v>0.3472</v>
+      </c>
+      <c r="L14" s="68"/>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G15),ISNUMBER(I15)),G15*I15,"")</f>
+        <v>0.3657</v>
+      </c>
+      <c r="L15" s="69"/>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G16),ISNUMBER(I16)),G16*I16,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="68"/>
+    </row>
+    <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="41" t="str">
+        <f aca="false">"   منزل متنوع   ·   "&amp;COUNTA(B19:B20)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D19:D20),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D19:D20),"#,##0")&amp;" د.ع"</f>
+        <v>   منزل متنوع   ·   2 منتجات   ·   السعر من 11,500 إلى 19,000 د.ع</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25"/>
+      <c r="H19" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G19),ISNUMBER(I19)),G19*I19,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="68"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G20),ISNUMBER(I20)),G20*I20,"")</f>
+        <v>0.4047</v>
+      </c>
+      <c r="L20" s="69"/>
+    </row>
+    <row r="21" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="53" t="str">
+        <f aca="false">"   السيارات (داش كام وإكسسوارات)   ·   "&amp;COUNTA(B23:B24)&amp;" منتجات   ·   السعر من "&amp;TEXT(MIN(D23:D24),"#,##0")&amp;" إلى "&amp;TEXT(MAX(D23:D24),"#,##0")&amp;" د.ع"</f>
+        <v>   السيارات (داش كام وإكسسوارات)   ·   2 منتجات   ·   السعر من 53,500 إلى 90,000 د.ع</v>
+      </c>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>53500</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>58500</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G23),ISNUMBER(I23)),G23*I23,"")</f>
+        <v>0.315</v>
+      </c>
+      <c r="L23" s="68"/>
+    </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="54" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G24),ISNUMBER(I24)),G24*I24,"")</f>
+        <v>0.284</v>
+      </c>
+      <c r="L24" s="69" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="L26" s="71" t="str">
+        <f aca="false">COUNTIF(L5:L24,"✅")&amp;" من "&amp;COUNTA(B5:B24)</f>
+        <v>1 من 11</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="62"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="B29:L29"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="B32:L32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G24">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I24">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K24">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF15803D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G6),ISNUMBER(I6)),G6*I6,"")</f>
+        <v>0.5893</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G7),ISNUMBER(I7)),G7*I7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G8),ISNUMBER(I8)),G8*I8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G9),ISNUMBER(I9)),G9*I9,"")</f>
+        <v>0.4047</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G10),ISNUMBER(I10)),G10*I10,"")</f>
+        <v>0.4221</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="54" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>53500</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G11),ISNUMBER(I11)),G11*I11,"")</f>
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>36000</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G12),ISNUMBER(I12)),G12*I12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G13),ISNUMBER(I13)),G13*I13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G14),ISNUMBER(I14)),G14*I14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G15),ISNUMBER(I15)),G15*I15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="57" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>29500</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="13" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G16),ISNUMBER(I16)),G16*I16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J19" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G19),ISNUMBER(I19)),G19*I19,"")</f>
+        <v>0.284</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>42500</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G20),ISNUMBER(I20)),G20*I20,"")</f>
+        <v>0.2688</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G21),ISNUMBER(I21)),G21*I21,"")</f>
+        <v>0.2714</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>26500</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G22),ISNUMBER(I22)),G22*I22,"")</f>
+        <v>0.3472</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>40500</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G23),ISNUMBER(I23)),G23*I23,"")</f>
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G24),ISNUMBER(I24)),G24*I24,"")</f>
+        <v>0.3657</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>37000</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G25),ISNUMBER(I25)),G25*I25,"")</f>
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="51" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <f aca="false">IF(AND(ISNUMBER(G28),ISNUMBER(I28)),G28*I28,"")</f>
+        <v>0.2214</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="20"/>
+      <c r="J29" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="22" t="str">
+        <f aca="false">IF(AND(ISNUMBER(G29),ISNUMBER(I29)),G29*I29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="B34:K34"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I29">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K29">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0.35"/>
+        <cfvo type="num" val="0.55"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFFDE68A"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF86EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF64748B"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I16"/>
@@ -4624,524 +5603,524 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="80" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
+      <c r="A1" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="81" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="81" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="81" t="s">
-        <v>176</v>
-      </c>
-      <c r="F3" s="81" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="81" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="81" t="s">
-        <v>179</v>
-      </c>
-      <c r="I3" s="81" t="s">
-        <v>180</v>
+      <c r="A3" s="82" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="82" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="82" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B6:B13)</f>
+      <c r="A4" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B6:B13)</f>
         <v>8</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D6:D13)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D6:D13)</f>
         <v>18000</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D6:D13)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D6:D13)</f>
         <v>101000</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D6:D13)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D6:D13)</f>
         <v>48937.5</v>
       </c>
-      <c r="F4" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I6:I13)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I6:I13)),--ISNUMBER(المنتجات!K6:K13))</f>
+      <c r="F4" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G6:G13)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G6:G13)),--ISNUMBER('المنتجات الأساسية'!I6:I13))</f>
         <v>4</v>
       </c>
-      <c r="G4" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I6:I13)=0,"-",MAX(المنتجات!I6:I13))</f>
+      <c r="G4" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G6:G13)=0,"-",MAX('المنتجات الأساسية'!G6:G13))</f>
         <v>0.83</v>
       </c>
-      <c r="H4" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K6:K13)=0,"-",MAX(المنتجات!K6:K13))</f>
+      <c r="H4" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I6:I13)=0,"-",MAX('المنتجات الأساسية'!I6:I13))</f>
         <v>0.71</v>
       </c>
-      <c r="I4" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M6:M13)=0,"-",MAX(المنتجات!M6:M13))</f>
+      <c r="I4" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K6:K13)=0,"-",MAX('المنتجات الأساسية'!K6:K13))</f>
         <v>0.5893</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B16:B17)</f>
+      <c r="A5" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B16:B17)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D16:D17)</f>
+      <c r="C5" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D16:D17)</f>
         <v>37000</v>
       </c>
-      <c r="D5" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D16:D17)</f>
+      <c r="D5" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D16:D17)</f>
         <v>47000</v>
       </c>
-      <c r="E5" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D16:D17)</f>
+      <c r="E5" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D16:D17)</f>
         <v>42000</v>
       </c>
-      <c r="F5" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I16:I17)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I16:I17)),--ISNUMBER(المنتجات!K16:K17))</f>
+      <c r="F5" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G16:G17)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G16:G17)),--ISNUMBER('المنتجات الأساسية'!I16:I17))</f>
         <v>1</v>
       </c>
-      <c r="G5" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I16:I17)=0,"-",MAX(المنتجات!I16:I17))</f>
+      <c r="G5" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G16:G17)=0,"-",MAX('المنتجات الأساسية'!G16:G17))</f>
         <v>0.5</v>
       </c>
-      <c r="H5" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K16:K17)=0,"-",MAX(المنتجات!K16:K17))</f>
+      <c r="H5" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I16:I17)=0,"-",MAX('المنتجات الأساسية'!I16:I17))</f>
         <v>0.62</v>
       </c>
-      <c r="I5" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M16:M17)=0,"-",MAX(المنتجات!M16:M17))</f>
+      <c r="I5" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K16:K17)=0,"-",MAX('المنتجات الأساسية'!K16:K17))</f>
         <v>0.31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="86" t="s">
-        <v>183</v>
-      </c>
-      <c r="B6" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B20:B23)</f>
+      <c r="A6" s="87" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B20:B23)</f>
         <v>4</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D20:D23)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D20:D23)</f>
         <v>26500</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D20:D23)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D20:D23)</f>
         <v>88500</v>
       </c>
       <c r="E6" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D20:D23)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D20:D23)</f>
         <v>49250</v>
       </c>
-      <c r="F6" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I20:I23)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I20:I23)),--ISNUMBER(المنتجات!K20:K23))</f>
+      <c r="F6" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G20:G23)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G20:G23)),--ISNUMBER('المنتجات الأساسية'!I20:I23))</f>
         <v>2</v>
       </c>
-      <c r="G6" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I20:I23)=0,"-",MAX(المنتجات!I20:I23))</f>
+      <c r="G6" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G20:G23)=0,"-",MAX('المنتجات الأساسية'!G20:G23))</f>
         <v>0.56</v>
       </c>
-      <c r="H6" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K20:K23)=0,"-",MAX(المنتجات!K20:K23))</f>
+      <c r="H6" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I20:I23)=0,"-",MAX('المنتجات الأساسية'!I20:I23))</f>
         <v>0.69</v>
       </c>
-      <c r="I6" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M20:M23)=0,"-",MAX(المنتجات!M20:M23))</f>
+      <c r="I6" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K20:K23)=0,"-",MAX('المنتجات الأساسية'!K20:K23))</f>
         <v>0.3657</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="87" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B26:B30)</f>
+      <c r="A7" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B26:B30)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D26:D30)</f>
+      <c r="C7" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D26:D30)</f>
         <v>21000</v>
       </c>
-      <c r="D7" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D26:D30)</f>
+      <c r="D7" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D26:D30)</f>
         <v>59000</v>
       </c>
-      <c r="E7" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D26:D30)</f>
+      <c r="E7" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D26:D30)</f>
         <v>36500</v>
       </c>
-      <c r="F7" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I26:I30)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I26:I30)),--ISNUMBER(المنتجات!K26:K30))</f>
+      <c r="F7" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G26:G30)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G26:G30)),--ISNUMBER('المنتجات الأساسية'!I26:I30))</f>
         <v>3</v>
       </c>
-      <c r="G7" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I26:I30)=0,"-",MAX(المنتجات!I26:I30))</f>
+      <c r="G7" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G26:G30)=0,"-",MAX('المنتجات الأساسية'!G26:G30))</f>
         <v>0.63</v>
       </c>
-      <c r="H7" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K26:K30)=0,"-",MAX(المنتجات!K26:K30))</f>
+      <c r="H7" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I26:I30)=0,"-",MAX('المنتجات الأساسية'!I26:I30))</f>
         <v>0.67</v>
       </c>
-      <c r="I7" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M26:M30)=0,"-",MAX(المنتجات!M26:M30))</f>
+      <c r="I7" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K26:K30)=0,"-",MAX('المنتجات الأساسية'!K26:K30))</f>
         <v>0.4221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="88" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B33:B34)</f>
+      <c r="A8" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B33:B34)</f>
         <v>2</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D33:D34)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D33:D34)</f>
         <v>29000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D33:D34)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D33:D34)</f>
         <v>60000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D33:D34)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D33:D34)</f>
         <v>44500</v>
       </c>
-      <c r="F8" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I33:I34)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I33:I34)),--ISNUMBER(المنتجات!K33:K34))</f>
+      <c r="F8" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G33:G34)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G33:G34)),--ISNUMBER('المنتجات الأساسية'!I33:I34))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!I33:I34)=0,"-",MAX(المنتجات!I33:I34))</f>
+      <c r="G8" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G33:G34)=0,"-",MAX('المنتجات الأساسية'!G33:G34))</f>
         <v>-</v>
       </c>
-      <c r="H8" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!K33:K34)=0,"-",MAX(المنتجات!K33:K34))</f>
+      <c r="H8" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I33:I34)=0,"-",MAX('المنتجات الأساسية'!I33:I34))</f>
         <v>-</v>
       </c>
-      <c r="I8" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!M33:M34)=0,"-",MAX(المنتجات!M33:M34))</f>
+      <c r="I8" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K33:K34)=0,"-",MAX('المنتجات الأساسية'!K33:K34))</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B37:B41)</f>
+      <c r="A9" s="90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B37:B41)</f>
         <v>5</v>
       </c>
-      <c r="C9" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D37:D41)</f>
+      <c r="C9" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D37:D41)</f>
         <v>11500</v>
       </c>
-      <c r="D9" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D37:D41)</f>
+      <c r="D9" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D37:D41)</f>
         <v>59000</v>
       </c>
-      <c r="E9" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D37:D41)</f>
+      <c r="E9" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D37:D41)</f>
         <v>26200</v>
       </c>
-      <c r="F9" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I37:I41)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I37:I41)),--ISNUMBER(المنتجات!K37:K41))</f>
+      <c r="F9" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G37:G41)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G37:G41)),--ISNUMBER('المنتجات الأساسية'!I37:I41))</f>
         <v>1</v>
       </c>
-      <c r="G9" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I37:I41)=0,"-",MAX(المنتجات!I37:I41))</f>
+      <c r="G9" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G37:G41)=0,"-",MAX('المنتجات الأساسية'!G37:G41))</f>
         <v>0.71</v>
       </c>
-      <c r="H9" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K37:K41)=0,"-",MAX(المنتجات!K37:K41))</f>
+      <c r="H9" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I37:I41)=0,"-",MAX('المنتجات الأساسية'!I37:I41))</f>
         <v>0.57</v>
       </c>
-      <c r="I9" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M37:M41)=0,"-",MAX(المنتجات!M37:M41))</f>
+      <c r="I9" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K37:K41)=0,"-",MAX('المنتجات الأساسية'!K37:K41))</f>
         <v>0.4047</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="90" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B44:B46)</f>
+      <c r="A10" s="91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B44:B46)</f>
         <v>3</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D44:D46)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D44:D46)</f>
         <v>41000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D44:D46)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D44:D46)</f>
         <v>62500</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D44:D46)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D44:D46)</f>
         <v>50500</v>
       </c>
-      <c r="F10" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I44:I46)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I44:I46)),--ISNUMBER(المنتجات!K44:K46))</f>
+      <c r="F10" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G44:G46)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G44:G46)),--ISNUMBER('المنتجات الأساسية'!I44:I46))</f>
         <v>1</v>
       </c>
-      <c r="G10" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I44:I46)=0,"-",MAX(المنتجات!I44:I46))</f>
+      <c r="G10" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G44:G46)=0,"-",MAX('المنتجات الأساسية'!G44:G46))</f>
         <v>0.76</v>
       </c>
-      <c r="H10" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!K44:K46)=0,"-",MAX(المنتجات!K44:K46))</f>
+      <c r="H10" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I44:I46)=0,"-",MAX('المنتجات الأساسية'!I44:I46))</f>
         <v>-</v>
       </c>
-      <c r="I10" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!M44:M46)=0,"-",MAX(المنتجات!M44:M46))</f>
+      <c r="I10" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K44:K46)=0,"-",MAX('المنتجات الأساسية'!K44:K46))</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="91" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B49:B50)</f>
+      <c r="A11" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B49:B50)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D49:D50)</f>
+      <c r="C11" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D49:D50)</f>
         <v>72000</v>
       </c>
-      <c r="D11" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D49:D50)</f>
+      <c r="D11" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D49:D50)</f>
         <v>81000</v>
       </c>
-      <c r="E11" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D49:D50)</f>
+      <c r="E11" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D49:D50)</f>
         <v>76500</v>
       </c>
-      <c r="F11" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I49:I50)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I49:I50)),--ISNUMBER(المنتجات!K49:K50))</f>
+      <c r="F11" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G49:G50)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G49:G50)),--ISNUMBER('المنتجات الأساسية'!I49:I50))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!I49:I50)=0,"-",MAX(المنتجات!I49:I50))</f>
+      <c r="G11" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G49:G50)=0,"-",MAX('المنتجات الأساسية'!G49:G50))</f>
         <v>-</v>
       </c>
-      <c r="H11" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!K49:K50)=0,"-",MAX(المنتجات!K49:K50))</f>
+      <c r="H11" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I49:I50)=0,"-",MAX('المنتجات الأساسية'!I49:I50))</f>
         <v>-</v>
       </c>
-      <c r="I11" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!M49:M50)=0,"-",MAX(المنتجات!M49:M50))</f>
+      <c r="I11" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K49:K50)=0,"-",MAX('المنتجات الأساسية'!K49:K50))</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B53:B56)</f>
+      <c r="A12" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B53:B56)</f>
         <v>4</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D53:D56)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D53:D56)</f>
         <v>22000</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D53:D56)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D53:D56)</f>
         <v>212000</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D53:D56)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D53:D56)</f>
         <v>75000</v>
       </c>
-      <c r="F12" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I53:I56)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I53:I56)),--ISNUMBER(المنتجات!K53:K56))</f>
+      <c r="F12" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G53:G56)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G53:G56)),--ISNUMBER('المنتجات الأساسية'!I53:I56))</f>
         <v>1</v>
       </c>
-      <c r="G12" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I53:I56)=0,"-",MAX(المنتجات!I53:I56))</f>
+      <c r="G12" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G53:G56)=0,"-",MAX('المنتجات الأساسية'!G53:G56))</f>
         <v>0.54</v>
       </c>
-      <c r="H12" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K53:K56)=0,"-",MAX(المنتجات!K53:K56))</f>
+      <c r="H12" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I53:I56)=0,"-",MAX('المنتجات الأساسية'!I53:I56))</f>
         <v>0.41</v>
       </c>
-      <c r="I12" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M53:M56)=0,"-",MAX(المنتجات!M53:M56))</f>
+      <c r="I12" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K53:K56)=0,"-",MAX('المنتجات الأساسية'!K53:K56))</f>
         <v>0.2214</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="93" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B59:B64)</f>
+      <c r="A13" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B59:B64)</f>
         <v>6</v>
       </c>
-      <c r="C13" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D59:D64)</f>
+      <c r="C13" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D59:D64)</f>
         <v>30000</v>
       </c>
-      <c r="D13" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D59:D64)</f>
+      <c r="D13" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D59:D64)</f>
         <v>90000</v>
       </c>
-      <c r="E13" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D59:D64)</f>
+      <c r="E13" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D59:D64)</f>
         <v>50000</v>
       </c>
-      <c r="F13" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I59:I64)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I59:I64)),--ISNUMBER(المنتجات!K59:K64))</f>
+      <c r="F13" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G59:G64)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G59:G64)),--ISNUMBER('المنتجات الأساسية'!I59:I64))</f>
         <v>6</v>
       </c>
-      <c r="G13" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!I59:I64)=0,"-",MAX(المنتجات!I59:I64))</f>
+      <c r="G13" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G59:G64)=0,"-",MAX('المنتجات الأساسية'!G59:G64))</f>
         <v>0.71</v>
       </c>
-      <c r="H13" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K59:K64)=0,"-",MAX(المنتجات!K59:K64))</f>
+      <c r="H13" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I59:I64)=0,"-",MAX('المنتجات الأساسية'!I59:I64))</f>
         <v>0.5</v>
       </c>
-      <c r="I13" s="22" t="n">
-        <f aca="false">IF(COUNT(المنتجات!M59:M64)=0,"-",MAX(المنتجات!M59:M64))</f>
+      <c r="I13" s="20" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K59:K64)=0,"-",MAX('المنتجات الأساسية'!K59:K64))</f>
         <v>0.315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94" t="s">
-        <v>191</v>
-      </c>
-      <c r="B14" s="83" t="n">
-        <f aca="false">COUNTA(المنتجات!B67:B70)</f>
+      <c r="A14" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="84" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B67:B70)</f>
         <v>4</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">MIN(المنتجات!D67:D70)</f>
+        <f aca="false">MIN('المنتجات الأساسية'!D67:D70)</f>
         <v>17000</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">MAX(المنتجات!D67:D70)</f>
+        <f aca="false">MAX('المنتجات الأساسية'!D67:D70)</f>
         <v>38500</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">AVERAGE(المنتجات!D67:D70)</f>
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D67:D70)</f>
         <v>29750</v>
       </c>
-      <c r="F14" s="83" t="n">
-        <f aca="false">COUNT(المنتجات!I67:I70)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I67:I70)),--ISNUMBER(المنتجات!K67:K70))</f>
+      <c r="F14" s="84" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G67:G70)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G67:G70)),--ISNUMBER('المنتجات الأساسية'!I67:I70))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!I67:I70)=0,"-",MAX(المنتجات!I67:I70))</f>
+      <c r="G14" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G67:G70)=0,"-",MAX('المنتجات الأساسية'!G67:G70))</f>
         <v>-</v>
       </c>
-      <c r="H14" s="30" t="n">
-        <f aca="false">IF(COUNT(المنتجات!K67:K70)=0,"-",MAX(المنتجات!K67:K70))</f>
+      <c r="H14" s="25" t="n">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I67:I70)=0,"-",MAX('المنتجات الأساسية'!I67:I70))</f>
         <v>0.67</v>
       </c>
-      <c r="I14" s="30" t="str">
-        <f aca="false">IF(COUNT(المنتجات!M67:M70)=0,"-",MAX(المنتجات!M67:M70))</f>
+      <c r="I14" s="25" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K67:K70)=0,"-",MAX('المنتجات الأساسية'!K67:K70))</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="95" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="85" t="n">
-        <f aca="false">COUNTA(المنتجات!B73:B74)</f>
+      <c r="A15" s="96" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="86" t="n">
+        <f aca="false">COUNTA('المنتجات الأساسية'!B73:B74)</f>
         <v>2</v>
       </c>
-      <c r="C15" s="20" t="n">
-        <f aca="false">MIN(المنتجات!D73:D74)</f>
+      <c r="C15" s="17" t="n">
+        <f aca="false">MIN('المنتجات الأساسية'!D73:D74)</f>
         <v>14000</v>
       </c>
-      <c r="D15" s="20" t="n">
-        <f aca="false">MAX(المنتجات!D73:D74)</f>
+      <c r="D15" s="17" t="n">
+        <f aca="false">MAX('المنتجات الأساسية'!D73:D74)</f>
         <v>15500</v>
       </c>
-      <c r="E15" s="20" t="n">
-        <f aca="false">AVERAGE(المنتجات!D73:D74)</f>
+      <c r="E15" s="17" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D73:D74)</f>
         <v>14750</v>
       </c>
-      <c r="F15" s="85" t="n">
-        <f aca="false">COUNT(المنتجات!I73:I74)+SUMPRODUCT(--NOT(ISNUMBER(المنتجات!I73:I74)),--ISNUMBER(المنتجات!K73:K74))</f>
+      <c r="F15" s="86" t="n">
+        <f aca="false">COUNT('المنتجات الأساسية'!G73:G74)+SUMPRODUCT(--NOT(ISNUMBER('المنتجات الأساسية'!G73:G74)),--ISNUMBER('المنتجات الأساسية'!I73:I74))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!I73:I74)=0,"-",MAX(المنتجات!I73:I74))</f>
+      <c r="G15" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!G73:G74)=0,"-",MAX('المنتجات الأساسية'!G73:G74))</f>
         <v>-</v>
       </c>
-      <c r="H15" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!K73:K74)=0,"-",MAX(المنتجات!K73:K74))</f>
+      <c r="H15" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!I73:I74)=0,"-",MAX('المنتجات الأساسية'!I73:I74))</f>
         <v>-</v>
       </c>
-      <c r="I15" s="22" t="str">
-        <f aca="false">IF(COUNT(المنتجات!M73:M74)=0,"-",MAX(المنتجات!M73:M74))</f>
+      <c r="I15" s="20" t="str">
+        <f aca="false">IF(COUNT('المنتجات الأساسية'!K73:K74)=0,"-",MAX('المنتجات الأساسية'!K73:K74))</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="96" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="96" t="n">
+      <c r="A16" s="97" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="97" t="n">
         <f aca="false">SUM(B4:B15)</f>
         <v>47</v>
       </c>
-      <c r="C16" s="97" t="n">
+      <c r="C16" s="98" t="n">
         <f aca="false">MIN(C4:C15)</f>
         <v>11500</v>
       </c>
-      <c r="D16" s="97" t="n">
+      <c r="D16" s="98" t="n">
         <f aca="false">MAX(D4:D15)</f>
         <v>212000</v>
       </c>
-      <c r="E16" s="97" t="n">
-        <f aca="false">AVERAGE(المنتجات!D5:D74)</f>
+      <c r="E16" s="98" t="n">
+        <f aca="false">AVERAGE('المنتجات الأساسية'!D5:D74)</f>
         <v>45276.5957446809</v>
       </c>
-      <c r="F16" s="96" t="n">
+      <c r="F16" s="97" t="n">
         <f aca="false">SUM(F4:F15)</f>
         <v>20</v>
       </c>
-      <c r="G16" s="98" t="n">
+      <c r="G16" s="99" t="n">
         <f aca="false">MAX(G4:G15)</f>
         <v>0.83</v>
       </c>
-      <c r="H16" s="98" t="n">
+      <c r="H16" s="99" t="n">
         <f aca="false">MAX(H4:H15)</f>
         <v>0.71</v>
       </c>
-      <c r="I16" s="98" t="n">
+      <c r="I16" s="99" t="n">
         <f aca="false">MAX(I4:I15)</f>
         <v>0.5893</v>
       </c>
